--- a/graficos/NMF_mejores_umass.xlsx
+++ b/graficos/NMF_mejores_umass.xlsx
@@ -46,33 +46,33 @@
     <t>porc_del_dominio</t>
   </si>
   <si>
+    <t>comisión</t>
+  </si>
+  <si>
+    <t>dictamen</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>comisión_dictamen_K3_4</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>comisión_dictamen_K3_2</t>
+  </si>
+  <si>
     <t>orps</t>
   </si>
   <si>
-    <t>dictamen</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>orps_dictamen_K3_2</t>
   </si>
   <si>
     <t>orps_dictamen_K3_4</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>orps_dictamen_K3_2</t>
-  </si>
-  <si>
-    <t>comisión</t>
-  </si>
-  <si>
-    <t>comisión_dictamen_K3_4</t>
-  </si>
-  <si>
-    <t>comisión_dictamen_K3_2</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
@@ -85,12 +85,12 @@
     <t>7</t>
   </si>
   <si>
+    <t>comisión_dictamen_K3_7</t>
+  </si>
+  <si>
     <t>orps_dictamen_K3_7</t>
   </si>
   <si>
-    <t>comisión_dictamen_K3_7</t>
-  </si>
-  <si>
     <t>orps_lim</t>
   </si>
   <si>
@@ -103,27 +103,27 @@
     <t>8</t>
   </si>
   <si>
+    <t>comisión_dictamen_K3_8</t>
+  </si>
+  <si>
     <t>orps_dictamen_K3_8</t>
   </si>
   <si>
-    <t>comisión_dictamen_K3_8</t>
+    <t>orps_lim_dictamen_K4_3</t>
   </si>
   <si>
     <t>orps_lim_dictamen_K4_7</t>
   </si>
   <si>
+    <t>orps_lim_dictamen_K4_5</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
     <t>orps_lim_dictamen_K4_1</t>
   </si>
   <si>
-    <t>orps_lim_dictamen_K4_3</t>
-  </si>
-  <si>
-    <t>orps_lim_dictamen_K4_5</t>
-  </si>
-  <si>
     <t>orps_lim_dictamen_K4_8</t>
   </si>
   <si>
@@ -133,10 +133,10 @@
     <t>orps_dictamen_K4_7</t>
   </si>
   <si>
+    <t>orps_dictamen_K4_5</t>
+  </si>
+  <si>
     <t>comisión_dictamen_K4_5</t>
-  </si>
-  <si>
-    <t>orps_dictamen_K4_5</t>
   </si>
 </sst>
 </file>
@@ -618,7 +618,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>17</v>
@@ -650,7 +650,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>18</v>
@@ -673,7 +673,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>11</v>
@@ -705,7 +705,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>11</v>
@@ -906,7 +906,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>31</v>
@@ -938,10 +938,10 @@
         <v>4</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="F14" s="3">
         <v>0.95</v>
@@ -970,10 +970,10 @@
         <v>4</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F15" s="3">
         <v>0.95</v>
@@ -1002,7 +1002,7 @@
         <v>4</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>35</v>
@@ -1057,7 +1057,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>11</v>
@@ -1089,7 +1089,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>11</v>
